--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-full-2.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-full-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68127BF4-DDC7-4206-896A-0DE110EA072F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{11D02A5C-9DAC-470F-B7B8-042375E05BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{003A78E3-FB39-4206-8A35-1B4526B34461}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{5C455BCD-354E-4025-9E93-96C3EA7ABB75}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="103" r:id="rId3"/>
+    <pivotCache cacheId="135" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576882060188" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{5C4AA387-2E61-49A5-A833-A1D775898004}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579454282408" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{DD6B2765-7BDA-4527-8F60-2232BE332400}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B8" sheet="Source"/>
   </cacheSource>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EF1E4FF3-57F3-475B-BDAD-9689C1C3FD47}" name="AllErrorPivot" cacheId="103" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E2C7308-F6F1-4396-90F8-56C2CF22C559}" name="AllErrorPivot" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -570,7 +570,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7A10A7D-3BE2-471A-ACC2-F9EF9ACF3474}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F577E8-3193-4AA8-B6D1-A68AD7E6F355}">
   <dimension ref="A4:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -616,7 +616,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CF949A2-7486-4475-9DB7-55CC3DC9CB25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F08C0A5-C808-4893-BBAF-80DE5B9A07BC}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
